--- a/trace_select_3.xlsx
+++ b/trace_select_3.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\桌面\数据\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7183732A-41FB-468A-941C-2390039A003A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE21CF32-170A-42EC-8567-EF0A551F76E4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10560" firstSheet="6" activeTab="7" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ALL" sheetId="1" r:id="rId1"/>
@@ -27,7 +27,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="519" uniqueCount="94">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="553" uniqueCount="95">
   <si>
     <t>file_name</t>
   </si>
@@ -351,6 +351,10 @@
   <si>
     <t>BfP</t>
     <phoneticPr fontId="10" type="noConversion"/>
+  </si>
+  <si>
+    <t>IO_time</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -4186,6 +4190,1257 @@
 </c:chartSpace>
 </file>
 
+<file path=xl/charts/chart7.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN"/>
+              <a:t>IO</a:t>
+            </a:r>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Baseline</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'RAID5+1'!$B$50:$I$50</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>web1_pre</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>hm_1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>lun_0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>lun_1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>lun_2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>usr_0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>hm_0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>wdev_0</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'RAID5+1'!$B$51:$I$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-1CFB-40B6-BE93-4343CBEC1E3F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>PPC</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'RAID5+1'!$B$50:$I$50</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>web1_pre</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>hm_1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>lun_0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>lun_1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>lun_2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>usr_0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>hm_0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>wdev_0</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'RAID5+1'!$B$52:$I$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1.0000033044256236</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.98656008518239047</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.99734889582259378</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.9959838780516026</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.97938143612500972</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.99487031759030686</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.98064165680871418</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.9964594259470112</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-1CFB-40B6-BE93-4343CBEC1E3F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Patch</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'RAID5+1'!$B$50:$I$50</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>web1_pre</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>hm_1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>lun_0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>lun_1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>lun_2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>usr_0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>hm_0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>wdev_0</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'RAID5+1'!$B$53:$I$53</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1.0000033044256236</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.98656008518239047</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.99756739555444074</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.99565801255313435</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.97996553478074921</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.99504733833754411</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.98065781271135033</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.9964594259470112</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-1CFB-40B6-BE93-4343CBEC1E3F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>BfP</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'RAID5+1'!$B$50:$I$50</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>web1_pre</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>hm_1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>lun_0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>lun_1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>lun_2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>usr_0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>hm_0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>wdev_0</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'RAID5+1'!$B$54:$I$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.26001153250664111</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.11405826919157315</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.92259169979877242</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.91181787662861657</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.83934142150664148</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.5505681679823976</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.59146209517602832</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.75498622513681457</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-1CFB-40B6-BE93-4343CBEC1E3F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="590183632"/>
+        <c:axId val="590180752"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="590183632"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="590180752"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="590180752"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="590183632"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/chart8.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="zh-CN"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:tx>
+        <c:rich>
+          <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:r>
+              <a:rPr lang="en-US" altLang="zh-CN"/>
+              <a:t>IO</a:t>
+            </a:r>
+            <a:endParaRPr lang="zh-CN" altLang="en-US"/>
+          </a:p>
+        </c:rich>
+      </c:tx>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:v>Baseline</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'RAID7+1'!$B$50:$I$50</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>web1_pre</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>hm_1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>lun_0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>lun_1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>lun_2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>usr_0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>hm_0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>wdev_0</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'RAID7+1'!$B$51:$I$51</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-BDFF-4649-9380-9AEED7F33A19}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:v>PPC</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'RAID7+1'!$B$50:$I$50</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>web1_pre</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>hm_1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>lun_0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>lun_1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>lun_2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>usr_0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>hm_0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>wdev_0</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'RAID7+1'!$B$52:$I$52</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.97361880018025238</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.99732503083036828</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.99913716169594557</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.000888676074805</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.0006064894311939</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.98910568519488473</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.0002720296926462</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-BDFF-4649-9380-9AEED7F33A19}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="2"/>
+          <c:order val="2"/>
+          <c:tx>
+            <c:v>Patch</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent3"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'RAID7+1'!$B$50:$I$50</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>web1_pre</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>hm_1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>lun_0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>lun_1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>lun_2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>usr_0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>hm_0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>wdev_0</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'RAID7+1'!$B$53:$I$53</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>1</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.97361880018025238</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.99664862889560013</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.99913716169594557</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>1.0004544735364838</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>1.0006064894311939</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.98873801745823242</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>1.0002720296926462</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-BDFF-4649-9380-9AEED7F33A19}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="3"/>
+          <c:order val="3"/>
+          <c:tx>
+            <c:v>BfP</c:v>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent4"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>'RAID7+1'!$B$50:$I$50</c:f>
+              <c:strCache>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>web1_pre</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>hm_1</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>lun_0</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>lun_1</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>lun_2</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>usr_0</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>hm_0</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>wdev_0</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>'RAID7+1'!$B$54:$I$54</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="8"/>
+                <c:pt idx="0">
+                  <c:v>0.2815837983318879</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>0.13931140766680739</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>0.88575753583038241</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>0.91096442075267881</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>0.8368243670888561</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>0.41402029408595548</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>0.58433425259704586</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>0.78501754376557031</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000003-BDFF-4649-9380-9AEED7F33A19}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="219"/>
+        <c:overlap val="-27"/>
+        <c:axId val="626980424"/>
+        <c:axId val="623559432"/>
+      </c:barChart>
+      <c:catAx>
+        <c:axId val="626980424"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="623559432"/>
+        <c:crosses val="autoZero"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="623559432"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="zh-CN"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="626980424"/>
+        <c:crosses val="autoZero"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:layout>
+        <c:manualLayout>
+          <c:xMode val="edge"/>
+          <c:yMode val="edge"/>
+          <c:x val="0.56702318460192469"/>
+          <c:y val="7.4652230971128566E-2"/>
+          <c:w val="0.38997134733158356"/>
+          <c:h val="7.8125546806649182E-2"/>
+        </c:manualLayout>
+      </c:layout>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="zh-CN"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="zh-CN"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
 <file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
   <a:schemeClr val="accent1"/>
@@ -4426,6 +5681,86 @@
 </cs:colorStyle>
 </file>
 
+<file path=xl/charts/colors7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/colors8.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
 <file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
@@ -6942,6 +8277,1012 @@
 </file>
 
 <file path=xl/charts/style6.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style7.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="65000"/>
+          <a:lumOff val="35000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/charts/style8.xml><?xml version="1.0" encoding="utf-8"?>
 <cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="201">
   <cs:axisTitle>
     <cs:lnRef idx="0"/>
@@ -7657,6 +9998,88 @@
       <a:graphic>
         <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
           <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId6"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>12</xdr:col>
+      <xdr:colOff>508000</xdr:colOff>
+      <xdr:row>36</xdr:row>
+      <xdr:rowOff>84364</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>20</xdr:col>
+      <xdr:colOff>217714</xdr:colOff>
+      <xdr:row>51</xdr:row>
+      <xdr:rowOff>106136</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="4" name="图表 3">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{16A7C68B-640C-A8C0-0BAF-02A32A7BD348}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
+</file>
+
+<file path=xl/drawings/drawing3.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>10</xdr:col>
+      <xdr:colOff>417286</xdr:colOff>
+      <xdr:row>33</xdr:row>
+      <xdr:rowOff>138793</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>18</xdr:col>
+      <xdr:colOff>127000</xdr:colOff>
+      <xdr:row>48</xdr:row>
+      <xdr:rowOff>160565</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="3" name="图表 2">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{A0E4E33E-B691-1244-B263-55D726089031}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
         </a:graphicData>
       </a:graphic>
     </xdr:graphicFrame>
@@ -17124,7 +19547,7 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3CEEEA87-302E-4EE5-812D-C1D210AF0EC2}">
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="2" max="2" width="10" bestFit="1" customWidth="1"/>
@@ -18208,16 +20631,332 @@
         <v>74</v>
       </c>
     </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="B45" s="14">
+        <v>153557700430</v>
+      </c>
+      <c r="C45" s="14">
+        <v>1285164437677</v>
+      </c>
+      <c r="D45" s="14">
+        <v>8427530287723</v>
+      </c>
+      <c r="E45" s="14">
+        <v>2051253907339</v>
+      </c>
+      <c r="F45" s="14">
+        <v>2164348540401</v>
+      </c>
+      <c r="G45" s="14">
+        <v>6532671418737</v>
+      </c>
+      <c r="H45" s="14">
+        <v>206089891725647</v>
+      </c>
+      <c r="I45" s="14">
+        <v>2302214330786</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9">
+      <c r="B46" s="14">
+        <v>153558207850</v>
+      </c>
+      <c r="C46" s="14">
+        <v>1267891937108</v>
+      </c>
+      <c r="D46" s="14">
+        <v>8405188026972</v>
+      </c>
+      <c r="E46" s="14">
+        <v>2043015821500</v>
+      </c>
+      <c r="F46" s="14">
+        <v>2119722781773</v>
+      </c>
+      <c r="G46" s="14">
+        <v>6499160889072</v>
+      </c>
+      <c r="H46" s="14">
+        <v>202100332873367</v>
+      </c>
+      <c r="I46" s="14">
+        <v>2294063170462</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9">
+      <c r="B47" s="14">
+        <v>153558207850</v>
+      </c>
+      <c r="C47" s="14">
+        <v>1267891937108</v>
+      </c>
+      <c r="D47" s="14">
+        <v>8407029440080</v>
+      </c>
+      <c r="E47" s="14">
+        <v>2042347388623</v>
+      </c>
+      <c r="F47" s="14">
+        <v>2120986974846</v>
+      </c>
+      <c r="G47" s="14">
+        <v>6500317307448</v>
+      </c>
+      <c r="H47" s="14">
+        <v>202103662441592</v>
+      </c>
+      <c r="I47" s="14">
+        <v>2294063170462</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="B48" s="14">
+        <v>39926773017</v>
+      </c>
+      <c r="C48" s="14">
+        <v>146583631388</v>
+      </c>
+      <c r="D48" s="14">
+        <v>7775169493256</v>
+      </c>
+      <c r="E48" s="14">
+        <v>1870369982216</v>
+      </c>
+      <c r="F48" s="14">
+        <v>1816627380536</v>
+      </c>
+      <c r="G48" s="14">
+        <v>3596680935045</v>
+      </c>
+      <c r="H48" s="14">
+        <v>121894359154652</v>
+      </c>
+      <c r="I48" s="14">
+        <v>1738140107056</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11">
+      <c r="B50" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11">
+      <c r="B51" s="8">
+        <v>1</v>
+      </c>
+      <c r="C51" s="8">
+        <v>1</v>
+      </c>
+      <c r="D51" s="8">
+        <v>1</v>
+      </c>
+      <c r="E51" s="8">
+        <v>1</v>
+      </c>
+      <c r="F51" s="8">
+        <v>1</v>
+      </c>
+      <c r="G51" s="8">
+        <v>1</v>
+      </c>
+      <c r="H51" s="8">
+        <v>1</v>
+      </c>
+      <c r="I51" s="8">
+        <v>1</v>
+      </c>
+      <c r="J51">
+        <f t="shared" ref="J51:J53" si="0">AVERAGE(B51:I51)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11">
+      <c r="B52" s="14">
+        <f>B46/B45</f>
+        <v>1.0000033044256236</v>
+      </c>
+      <c r="C52" s="14">
+        <f t="shared" ref="C52:I52" si="1">C46/C45</f>
+        <v>0.98656008518239047</v>
+      </c>
+      <c r="D52" s="14">
+        <f t="shared" si="1"/>
+        <v>0.99734889582259378</v>
+      </c>
+      <c r="E52" s="14">
+        <f t="shared" si="1"/>
+        <v>0.9959838780516026</v>
+      </c>
+      <c r="F52" s="14">
+        <f t="shared" si="1"/>
+        <v>0.97938143612500972</v>
+      </c>
+      <c r="G52" s="14">
+        <f t="shared" si="1"/>
+        <v>0.99487031759030686</v>
+      </c>
+      <c r="H52" s="14">
+        <f t="shared" si="1"/>
+        <v>0.98064165680871418</v>
+      </c>
+      <c r="I52" s="14">
+        <f t="shared" si="1"/>
+        <v>0.9964594259470112</v>
+      </c>
+      <c r="J52">
+        <f t="shared" si="0"/>
+        <v>0.99140612499415659</v>
+      </c>
+      <c r="K52" s="14">
+        <f>J52-J54</f>
+        <v>0.37330146400322095</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11">
+      <c r="B53">
+        <f>B47/B45</f>
+        <v>1.0000033044256236</v>
+      </c>
+      <c r="C53">
+        <f t="shared" ref="C53:I53" si="2">C47/C45</f>
+        <v>0.98656008518239047</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="2"/>
+        <v>0.99756739555444074</v>
+      </c>
+      <c r="E53">
+        <f t="shared" si="2"/>
+        <v>0.99565801255313435</v>
+      </c>
+      <c r="F53">
+        <f t="shared" si="2"/>
+        <v>0.97996553478074921</v>
+      </c>
+      <c r="G53">
+        <f t="shared" si="2"/>
+        <v>0.99504733833754411</v>
+      </c>
+      <c r="H53">
+        <f t="shared" si="2"/>
+        <v>0.98065781271135033</v>
+      </c>
+      <c r="I53">
+        <f t="shared" si="2"/>
+        <v>0.9964594259470112</v>
+      </c>
+      <c r="J53">
+        <f t="shared" si="0"/>
+        <v>0.99148986368653058</v>
+      </c>
+      <c r="K53">
+        <f>J53-J54</f>
+        <v>0.37338520269559494</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11">
+      <c r="B54">
+        <f>B48/B45</f>
+        <v>0.26001153250664111</v>
+      </c>
+      <c r="C54">
+        <f t="shared" ref="C54:I54" si="3">C48/C45</f>
+        <v>0.11405826919157315</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="3"/>
+        <v>0.92259169979877242</v>
+      </c>
+      <c r="E54">
+        <f t="shared" si="3"/>
+        <v>0.91181787662861657</v>
+      </c>
+      <c r="F54">
+        <f t="shared" si="3"/>
+        <v>0.83934142150664148</v>
+      </c>
+      <c r="G54">
+        <f t="shared" si="3"/>
+        <v>0.5505681679823976</v>
+      </c>
+      <c r="H54">
+        <f t="shared" si="3"/>
+        <v>0.59146209517602832</v>
+      </c>
+      <c r="I54">
+        <f t="shared" si="3"/>
+        <v>0.75498622513681457</v>
+      </c>
+      <c r="J54">
+        <f>AVERAGE(B54:I54)</f>
+        <v>0.61810466099093564</v>
+      </c>
+      <c r="K54">
+        <f>J51-J54</f>
+        <v>0.38189533900906436</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{6F7977BA-D8E5-419B-B2A5-BA558B8AFED5}">
-  <dimension ref="A1:I42"/>
+  <dimension ref="A1:K54"/>
   <sheetFormatPr defaultRowHeight="14"/>
   <cols>
     <col min="2" max="5" width="13.7265625" bestFit="1" customWidth="1"/>
@@ -19303,9 +22042,325 @@
         <v>74</v>
       </c>
     </row>
+    <row r="44" spans="1:9">
+      <c r="A44" s="2" t="s">
+        <v>94</v>
+      </c>
+      <c r="B44" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C44" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D44" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E44" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F44" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G44" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H44" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I44" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9">
+      <c r="B45" s="7">
+        <v>137379649984</v>
+      </c>
+      <c r="C45" s="7">
+        <v>662713348614</v>
+      </c>
+      <c r="D45" s="7">
+        <v>2181155589843</v>
+      </c>
+      <c r="E45" s="7">
+        <v>1738046235260</v>
+      </c>
+      <c r="F45" s="7">
+        <v>2020166085144</v>
+      </c>
+      <c r="G45" s="7">
+        <v>4147371147175</v>
+      </c>
+      <c r="H45" s="7">
+        <v>159118863726434</v>
+      </c>
+      <c r="I45" s="7">
+        <v>1817473791889</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" ht="14.5">
+      <c r="B46" s="7">
+        <v>137379649984</v>
+      </c>
+      <c r="C46" s="14">
+        <v>645230175341</v>
+      </c>
+      <c r="D46" s="14">
+        <v>2175321065886</v>
+      </c>
+      <c r="E46" s="14">
+        <v>1736546582394</v>
+      </c>
+      <c r="F46" s="14">
+        <v>2021961358411</v>
+      </c>
+      <c r="G46" s="14">
+        <v>4149886483943</v>
+      </c>
+      <c r="H46" s="14">
+        <v>157385372733566</v>
+      </c>
+      <c r="I46" s="14">
+        <v>1817968198726</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" ht="14.5">
+      <c r="B47" s="7">
+        <v>137379649984</v>
+      </c>
+      <c r="C47" s="14">
+        <v>645230175341</v>
+      </c>
+      <c r="D47" s="14">
+        <v>2173845728025</v>
+      </c>
+      <c r="E47" s="14">
+        <v>1736546582394</v>
+      </c>
+      <c r="F47" s="14">
+        <v>2021084197169</v>
+      </c>
+      <c r="G47" s="14">
+        <v>4149886483943</v>
+      </c>
+      <c r="H47" s="14">
+        <v>157326869861081</v>
+      </c>
+      <c r="I47" s="14">
+        <v>1817968198726</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9">
+      <c r="B48" s="14">
+        <v>38683883656</v>
+      </c>
+      <c r="C48" s="14">
+        <v>92323529475</v>
+      </c>
+      <c r="D48" s="14">
+        <v>1931975000522</v>
+      </c>
+      <c r="E48" s="14">
+        <v>1583298281945</v>
+      </c>
+      <c r="F48" s="14">
+        <v>1690524205615</v>
+      </c>
+      <c r="G48" s="14">
+        <v>1717095822037</v>
+      </c>
+      <c r="H48" s="14">
+        <v>92978602309677</v>
+      </c>
+      <c r="I48" s="14">
+        <v>1426748811967</v>
+      </c>
+    </row>
+    <row r="50" spans="2:11">
+      <c r="B50" s="8" t="s">
+        <v>62</v>
+      </c>
+      <c r="C50" s="8" t="s">
+        <v>59</v>
+      </c>
+      <c r="D50" s="8" t="s">
+        <v>79</v>
+      </c>
+      <c r="E50" s="8" t="s">
+        <v>80</v>
+      </c>
+      <c r="F50" s="8" t="s">
+        <v>81</v>
+      </c>
+      <c r="G50" s="8" t="s">
+        <v>60</v>
+      </c>
+      <c r="H50" s="8" t="s">
+        <v>58</v>
+      </c>
+      <c r="I50" s="8" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="51" spans="2:11">
+      <c r="B51" s="7">
+        <v>1</v>
+      </c>
+      <c r="C51" s="7">
+        <v>1</v>
+      </c>
+      <c r="D51" s="7">
+        <v>1</v>
+      </c>
+      <c r="E51" s="7">
+        <v>1</v>
+      </c>
+      <c r="F51" s="7">
+        <v>1</v>
+      </c>
+      <c r="G51" s="7">
+        <v>1</v>
+      </c>
+      <c r="H51" s="7">
+        <v>1</v>
+      </c>
+      <c r="I51" s="7">
+        <v>1</v>
+      </c>
+      <c r="J51">
+        <f t="shared" ref="J51:J53" si="0">AVERAGE(B51:I51)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="2:11">
+      <c r="B52">
+        <f>B46/B45</f>
+        <v>1</v>
+      </c>
+      <c r="C52">
+        <f t="shared" ref="C52:I52" si="1">C46/C45</f>
+        <v>0.97361880018025238</v>
+      </c>
+      <c r="D52">
+        <f t="shared" si="1"/>
+        <v>0.99732503083036828</v>
+      </c>
+      <c r="E52">
+        <f t="shared" si="1"/>
+        <v>0.99913716169594557</v>
+      </c>
+      <c r="F52">
+        <f t="shared" si="1"/>
+        <v>1.000888676074805</v>
+      </c>
+      <c r="G52">
+        <f t="shared" si="1"/>
+        <v>1.0006064894311939</v>
+      </c>
+      <c r="H52">
+        <f t="shared" si="1"/>
+        <v>0.98910568519488473</v>
+      </c>
+      <c r="I52">
+        <f t="shared" si="1"/>
+        <v>1.0002720296926462</v>
+      </c>
+      <c r="J52">
+        <f t="shared" si="0"/>
+        <v>0.99511923413751202</v>
+      </c>
+      <c r="K52" s="2">
+        <f>J52-J54</f>
+        <v>0.390392531622614</v>
+      </c>
+    </row>
+    <row r="53" spans="2:11">
+      <c r="B53">
+        <f>B47/B45</f>
+        <v>1</v>
+      </c>
+      <c r="C53">
+        <f t="shared" ref="C53:I53" si="2">C47/C45</f>
+        <v>0.97361880018025238</v>
+      </c>
+      <c r="D53">
+        <f t="shared" si="2"/>
+        <v>0.99664862889560013</v>
+      </c>
+      <c r="E53">
+        <f t="shared" si="2"/>
+        <v>0.99913716169594557</v>
+      </c>
+      <c r="F53">
+        <f t="shared" si="2"/>
+        <v>1.0004544735364838</v>
+      </c>
+      <c r="G53">
+        <f t="shared" si="2"/>
+        <v>1.0006064894311939</v>
+      </c>
+      <c r="H53">
+        <f t="shared" si="2"/>
+        <v>0.98873801745823242</v>
+      </c>
+      <c r="I53">
+        <f t="shared" si="2"/>
+        <v>1.0002720296926462</v>
+      </c>
+      <c r="J53">
+        <f t="shared" si="0"/>
+        <v>0.99493445011129433</v>
+      </c>
+      <c r="K53">
+        <f>J52-J54</f>
+        <v>0.390392531622614</v>
+      </c>
+    </row>
+    <row r="54" spans="2:11">
+      <c r="B54">
+        <f>B48/B45</f>
+        <v>0.2815837983318879</v>
+      </c>
+      <c r="C54">
+        <f t="shared" ref="C54:I54" si="3">C48/C45</f>
+        <v>0.13931140766680739</v>
+      </c>
+      <c r="D54">
+        <f t="shared" si="3"/>
+        <v>0.88575753583038241</v>
+      </c>
+      <c r="E54">
+        <f t="shared" si="3"/>
+        <v>0.91096442075267881</v>
+      </c>
+      <c r="F54">
+        <f t="shared" si="3"/>
+        <v>0.8368243670888561</v>
+      </c>
+      <c r="G54">
+        <f t="shared" si="3"/>
+        <v>0.41402029408595548</v>
+      </c>
+      <c r="H54">
+        <f t="shared" si="3"/>
+        <v>0.58433425259704586</v>
+      </c>
+      <c r="I54">
+        <f t="shared" si="3"/>
+        <v>0.78501754376557031</v>
+      </c>
+      <c r="J54">
+        <f>AVERAGE(B54:I54)</f>
+        <v>0.60472670251489802</v>
+      </c>
+      <c r="K54">
+        <f>J51-J54</f>
+        <v>0.39527329748510198</v>
+      </c>
+    </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>